--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_midpoint_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_midpoint_fix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C3DD55-2BAA-4635-B704-3779C14D24A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31FFFFD-76A7-404F-9C10-1EC76E3EA07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3431,7 +3431,7 @@
         <v>8.5400278439493646E-7</v>
       </c>
       <c r="F49">
-        <v>1.3067825697362419E-2</v>
+        <v>1.27271106466651E-2</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
@@ -3443,22 +3443,22 @@
         <v>281.25</v>
       </c>
       <c r="J49">
-        <v>0.56982129812240601</v>
+        <v>0.56852781772613525</v>
       </c>
       <c r="K49">
-        <v>0.32469633221626282</v>
+        <v>0.32322388887405401</v>
       </c>
       <c r="L49">
-        <v>4.0292450396687456E-3</v>
+        <v>4.0200987520733972E-3</v>
       </c>
       <c r="M49">
-        <v>8.0584902316331863E-3</v>
+        <v>8.0401971936225891E-3</v>
       </c>
       <c r="N49">
         <v>6.5852441356106795E-4</v>
       </c>
       <c r="O49">
-        <v>176.50796041457949</v>
+        <v>181.2332213438458</v>
       </c>
       <c r="P49">
         <v>70</v>

--- a/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_midpoint_fix.xlsx
+++ b/DDM GD Find Alpha Rebuild/all_deme_alpha_results_summary_midpoint_fix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\DDM GD Find Alpha Rebuild\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31FFFFD-76A7-404F-9C10-1EC76E3EA07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC99519-C9E5-484A-BE2D-57F713E3D2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S102"/>
+  <dimension ref="A1:S103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -6707,6 +6707,12 @@
         <v>2.6295130237229319E-2</v>
       </c>
     </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S103">
+        <f>AVERAGE(S2:S102)</f>
+        <v>0.28265657141917938</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
